--- a/assets/constructions/examples/ctd_mih_rou.xlsx
+++ b/assets/constructions/examples/ctd_mih_rou.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,54 +584,66 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M200D32Z04M16RN10</t>
+          <t>TRS-5R25-M12-2T</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M200</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>32</v>
-      </c>
+          <t>TRS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="N2" t="n">
-        <v>48300</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -639,96 +651,118 @@
       <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>RPMW1003</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>WIDIA_RN10T3H</t>
+          <t>DER_RP1003H</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>M16</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>24</v>
-      </c>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>WID_RN10T3_H</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>WID_M200D3_942</t>
-        </is>
-      </c>
+          <t>RP1003_H</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2017 / WIDIA достижения</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>4494.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRS-5R35-M16-3T</t>
+          <t>12391050400</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TRS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>M100</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>52</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="N3" t="n">
+        <v>22000</v>
+      </c>
       <c r="O3" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -736,106 +770,110 @@
       <c r="Q3" t="n">
         <v>5</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>RPMW1003</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>DER_RP1003H</t>
+          <t>WIDIA_RD1003H</t>
         </is>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>M16</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>19</v>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RP1003_H</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+          <t>WID_RD1003_H</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>WID_123910_3316</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT100-025G12R03RD10</t>
+          <t>TRS-4R16-M8-2T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MT100-G...RD10</t>
+          <t>TRS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>52</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RDN..10T3MO..N</t>
+          <t>RDMT0802</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -843,12 +881,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M12</t>
+          <t>METRIC_THREAD:M8</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SKIF_RD10T3H</t>
+          <t>DER_RD0802H</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -865,156 +903,176 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>17</v>
-      </c>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>SKIF_RD10T3H</t>
+          <t>RD0802_H</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>4037.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT100-025G12R02RD12</t>
+          <t>M200D125Z03M16RN10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MT100-G...RD12</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>M200</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>31.75</v>
+      </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>21.75</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>57</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48500</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>METRIC_THREAD:M16</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>WIDIA_RN10T3H</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>RDN..1204MO..N</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>METRIC_THREAD:M12</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SKIF_RD1204H</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M16</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>SKIF_RD1204H</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+          <t>WID_RN10T3_H</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>WID_M200D1_793</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2019 / Novo</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M170D032Z02M16RD16</t>
+          <t>020R33690-02-05-M10032</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>M170</t>
-        </is>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>16</v>
-      </c>
-      <c r="F6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" t="n">
-        <v>29</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -1022,39 +1080,41 @@
       <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>20</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9950</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>RP…10T3 M0E</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M10</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>WIDIA_RD1604H</t>
+          <t>PALB_RD10T3H</t>
         </is>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
@@ -1063,27 +1123,31 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>M16</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>22</v>
-      </c>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>WID_RD1604_H</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>WID_M170D0_653</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
-        </is>
+          <t>2022/PALBIT Главный каталог</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>223.46</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>20543.5</v>
       </c>
     </row>
   </sheetData>
